--- a/471/food/tm2026-sm.xlsx
+++ b/471/food/tm2026-sm.xlsx
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C1" s="57" t="inlineStr">
         <is>
-          <t>МБОУ «Гудермесская СШ №1 им. Тимиралиева М.Х.»</t>
+          <t xml:space="preserve">МБОУ «Гудермесская СШ №1 им. Тимиралиева М.Х.» </t>
         </is>
       </c>
       <c r="D1" s="60" t="n"/>
